--- a/files/AI+Project+Work+Item+Defintitions.xlsx
+++ b/files/AI+Project+Work+Item+Defintitions.xlsx
@@ -255,7 +255,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +274,12 @@
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -361,7 +367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -384,8 +390,8 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -405,16 +411,22 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -725,11 +737,11 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="7.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="21.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="19" width="76.57642857142856" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="19" width="106.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="19" width="77.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="19" width="7.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="19" width="21.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="20" width="76.57642857142856" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="20" width="106.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="21" width="77.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="25.5">
@@ -749,7 +761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="44.25">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="46.5">
       <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
@@ -764,7 +776,7 @@
       </c>
       <c r="E2" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="57">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="73.5">
       <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
@@ -779,7 +791,7 @@
       </c>
       <c r="E3" s="8"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="134.25">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="155.25">
       <c r="A4" s="9" t="s">
         <v>14</v>
       </c>
